--- a/docs/引脚分配表.xlsx
+++ b/docs/引脚分配表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="37">
   <si>
     <t>模块</t>
   </si>
@@ -106,13 +106,13 @@
     <t>3.3V供电，输出安全</t>
   </si>
   <si>
-    <t>有源蜂鸣器（低电平触发）</t>
+    <t>无源蜂鸣器（高电平触发）</t>
   </si>
   <si>
     <t>I/O (控制端)</t>
   </si>
   <si>
-    <t>PA6(TIM3_CH1)</t>
+    <t>PA11</t>
   </si>
   <si>
     <t>使用 PWM 控制音调</t>
@@ -121,19 +121,25 @@
     <t>LED</t>
   </si>
   <si>
+    <t>正极长脚</t>
+  </si>
+  <si>
+    <t>先接1k电阻再接PB12</t>
+  </si>
+  <si>
+    <t>串联一个 1k 限流电阻</t>
+  </si>
+  <si>
+    <t>负极短脚</t>
+  </si>
+  <si>
+    <t>按键 * 6</t>
+  </si>
+  <si>
     <t>信号端</t>
   </si>
   <si>
-    <t>PB12</t>
-  </si>
-  <si>
-    <t>串联一个 1k 限流电阻</t>
-  </si>
-  <si>
-    <t>按键 * 6</t>
-  </si>
-  <si>
-    <t>PB13/PB15/PA11/PA15/PB5/PB7</t>
+    <t>PB13/PB15/PA12/PB3/PB5/PB7</t>
   </si>
   <si>
     <t>另一端接 GND (开启内部上拉)</t>
@@ -1419,7 +1425,7 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
@@ -1430,16 +1436,16 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1460,7 +1466,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B21 D21 A17:D17 B16 D15:D16 B10 A11:D11 A12:B12 B13:D13 A14:D14 A15:B15 A18:B18 D18:D19 B19 A20:D20 A22:D22 D8:D9 A8:B9 B6:D6 A7:D7 D4 A4:B5 A1 D1 B2:D2 A3:D3" numberStoredAsText="1"/>
+    <ignoredError sqref="A3:D3 B2:D2 D1 A1 A4:B5 D4 A7:D7 B6:D6 A8:B9 D8:D9 A22:D22 A20 C20:D20 D18:D19 A18:B18 A15:B15 A14:D14 B13:D13 A12:B12 A11:D11 B10 D15:D16 B16 A17:D17 D21 B21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/引脚分配表.xlsx
+++ b/docs/引脚分配表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
   <si>
     <t>模块</t>
   </si>
@@ -46,6 +46,21 @@
     <t>电源/电平说明</t>
   </si>
   <si>
+    <t>STM32</t>
+  </si>
+  <si>
+    <t>VCC 5V</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>用电源模块MB102给5V引脚供电，经板载LOD稳压，供电更加稳定</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
     <t>OLED 0.96寸</t>
   </si>
   <si>
@@ -58,9 +73,6 @@
     <t/>
   </si>
   <si>
-    <t>GND</t>
-  </si>
-  <si>
     <t>SCL</t>
   </si>
   <si>
@@ -82,9 +94,6 @@
     <t>MQ-2 烟雾</t>
   </si>
   <si>
-    <t>5V</t>
-  </si>
-  <si>
     <t>必须接 5V</t>
   </si>
   <si>
@@ -112,7 +121,7 @@
     <t>I/O (控制端)</t>
   </si>
   <si>
-    <t>PA11</t>
+    <t>PA10</t>
   </si>
   <si>
     <t>使用 PWM 控制音调</t>
@@ -139,7 +148,7 @@
     <t>信号端</t>
   </si>
   <si>
-    <t>PB13/PB15/PA12/PB3/PB5/PB7</t>
+    <t>PB15/PA9/PB3/PB5/PB7/PB9</t>
   </si>
   <si>
     <t>另一端接 GND (开启内部上拉)</t>
@@ -1148,13 +1157,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="30.25" customWidth="1"/>
-    <col min="4" max="4" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1186,137 +1195,131 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -1324,149 +1327,177 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
         <v>33</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>34</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A3:D3 B2:D2 D1 A1 A4:B5 D4 A7:D7 B6:D6 A8:B9 D8:D9 A22:D22 A20 C20:D20 D18:D19 A18:B18 A15:B15 A14:D14 B13:D13 A12:B12 A11:D11 B10 D15:D16 B16 A17:D17 D21 B21" numberStoredAsText="1"/>
+    <ignoredError sqref="A5:D5 B4:D4 D1 A1 A6:B7 D6 A9:D9 B8:D8 A10:B11 D10:D11 A24:D24 A22 C22:D22 D20:D21 A20:B20 A17:B17 A16:D16 B15:D15 A14:B14 A13:D13 B12 D17:D18 B18 A19:D19 D23 B23" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/引脚分配表.xlsx
+++ b/docs/引脚分配表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20160" windowHeight="11535"/>
+    <workbookView windowWidth="19065" windowHeight="11670"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="50">
   <si>
     <t>模块</t>
   </si>
@@ -121,10 +121,40 @@
     <t>I/O (控制端)</t>
   </si>
   <si>
-    <t>PA10</t>
+    <t>PB1</t>
   </si>
   <si>
     <t>使用 PWM 控制音调</t>
+  </si>
+  <si>
+    <t>MicroSD卡模块</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>PA4</t>
+  </si>
+  <si>
+    <t>SCK</t>
+  </si>
+  <si>
+    <t>PA5</t>
+  </si>
+  <si>
+    <t>MISO</t>
+  </si>
+  <si>
+    <t>PA6</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>PA7</t>
+  </si>
+  <si>
+    <t>模块要求必须接5V</t>
   </si>
   <si>
     <t>LED</t>
@@ -1157,7 +1187,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
@@ -1403,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
@@ -1447,49 +1477,103 @@
       <c r="C21" t="s">
         <v>33</v>
       </c>
-      <c r="D21" t="s">
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>35</v>
       </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" t="s">
         <v>38</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
+    <row r="25" spans="1:4">
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1497,7 +1581,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A5:D5 B4:D4 D1 A1 A6:B7 D6 A9:D9 B8:D8 A10:B11 D10:D11 A24:D24 A22 C22:D22 D20:D21 A20:B20 A17:B17 A16:D16 B15:D15 A14:B14 A13:D13 B12 D17:D18 B18 A19:D19 D23 B23" numberStoredAsText="1"/>
+    <ignoredError sqref="D27 B29 D29 A19:D19 B18 D17:D18 B12 A13:D13 A14:B14 B15:D15 A16:D16 A17:B17 A20:B20 D20 C28:D28 A28 A30:D30 D10:D11 A10:B11 B8:D8 A9:D9 D6 A6:B7 A1 D1 B4:D4 A5:D5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/引脚分配表.xlsx
+++ b/docs/引脚分配表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
   <si>
     <t>模块</t>
   </si>
@@ -142,16 +142,19 @@
     <t>PA5</t>
   </si>
   <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>PA7</t>
+  </si>
+  <si>
     <t>MISO</t>
   </si>
   <si>
     <t>PA6</t>
   </si>
   <si>
-    <t>MOSI</t>
-  </si>
-  <si>
-    <t>PA7</t>
+    <t>必须接PA6</t>
   </si>
   <si>
     <t>模块要求必须接5V</t>
@@ -1501,6 +1504,9 @@
       <c r="C24" t="s">
         <v>39</v>
       </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" t="s">
@@ -1510,7 +1516,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1523,16 +1529,16 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1540,7 +1546,7 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
@@ -1551,16 +1557,16 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:4">
